--- a/outputs/matching_results.xlsx
+++ b/outputs/matching_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,100 +483,230 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4353487</t>
+          <t>13996438</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陈婕</t>
+          <t>张佳骏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8fe7c852-fc41-4ab1-a45d-db522f9a9b41</t>
+          <t>25104d61-392a-4546-862b-46d16bdbf9b6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounting Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bachelor’s degree in Accounting, Finance, or a related field, 5+ years of progressive accounting experience, 2+ years in a supervisory or management role, Advanced proficiency in Microsoft Excel, Experience using ERP systems</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Exceptional leadership, communication, analytical, and problem-solving skills</t>
+          <t>经验年限, 人力资源管理知识, 招聘与保留策略, 员工关系管理, HRIS软件熟练度</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Consider for an interview, but be aware to assess for leadership and communication skills.</t>
+          <t>建议寻找具有人力资源背景和经验的候选人。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Over 8 years of experience in accounting, including 4 years as a general ledger accountant and currently as a finance department head.; Strong knowledge of various accounting standards and financial reporting.; Practical experience with ERP systems, including developing and implementing software.; Proven ability to manage accounting operations and lead teams.</t>
+          <t>五年会计工作经验; 良好的问题解决能力; 详细和细致的工作习惯</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>While the candidate has strong experience, specific metrics or examples of leadership and communication skills were not detailed in the CV.; No accounting designation like CPA, CMA, or CGA as preferred in the job description.</t>
+          <t>缺乏人力资源管理经验; 不符合岗位要求的学历背景; 未持有相关的HR专业认证</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>4353487</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>陈婕</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25104d61-392a-4546-862b-46d16bdbf9b6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>财务, 经济学, 会计</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Human Resources or related field, 3 to 5+ years in HR roles, Certifications (CHRP, SHRM-CP), Employee Relations, Talent Management, HRIS proficiency</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Candidate is recommended for financial roles, but not suitable for the HR Manager position.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Extensive experience in financial management; Strong accounting and financial software skills; Good English proficiency (reading and writing)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No relevant HR experience; Lacks required educational background in HR or related fields; No certifications related to HR; Limited experience in employee relations or talent management; Does not meet the job's minimum years of HR experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>4556029</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>曹珺</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8fe7c852-fc41-4ab1-a45d-db522f9a9b41</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Accounting Manager</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>68</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>财务分析, 会计, 审计</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2+ years in a supervisory or management role, Advanced proficiency in Microsoft Excel, Experience using ERP systems (e.g., NetSuite, SAP) or accounting software (e.g., QuickBooks, Sage), Professional accounting designation (e.g., CPA, CMA, or CGA)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Consider for a role with lower management responsibilities or additional mentoring to fulfill leadership requirements.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9 years of work experience including 6 years in Fortune 500 companies; Strong experience in accounting and auditing tasks; Fluent in English, which supports communication in diverse teams</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Lacks supervisory or management experience for 2+ years as required; No experience mentioned with advanced Excel functionalities or ERP systems; No professional accounting designation, which is preferred for the role</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25104d61-392a-4546-862b-46d16bdbf9b6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Human Resources, Business Administration, or a related field, 3 to 5+ years of HR experience, Certifications like CHRP or CHRL or SHRM-CP/PHR, Employee Relations skills, Talent Management experience, Communication and Ethics skills, Proficiency with HRIS software</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Consider for finance-related positions, but not suitable for HR Manager role.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Significant mismatch between candidate's background in finance/accounting and the HR management role; Lack of required HR experience and qualifications; No relevant certifications for HR field; Absence of experience in employee relations and talent management</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>13234064</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>郝秋君</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25104d61-392a-4546-862b-46d16bdbf9b6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Human Resources or Business Administration, 5+ years of HR experience, Knowledge of conflict resolution and performance management, Experience in recruitment, onboarding, and retention strategies, Proficiency with HRIS and payroll systems</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Not a suitable match for the HR Manager position.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Proficiency in English; Strong accounting background; Familiarity with MS Office and SAP systems</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lack of relevant HR experience; No formal education in Human Resources or related field; Missing required HR certifications and skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6497826</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>孙雯彬</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25104d61-392a-4546-862b-46d16bdbf9b6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HR experience, HR management skills, Employee Relations, Talent Management, HR certifications</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Not a suitable fit for the HR Manager position.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Over 8 years of accounting and finance experience; Proficient in SAP; Strong analytical skills; Experience in managing accounts payable; Ability to coordinate with entities such as tax authorities</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No relevant HR experience or education; Does not meet the required experience years in an HR role; Lacks necessary HR certifications; Skills primarily focused on accounting rather than HR practices</t>
         </is>
       </c>
     </row>
